--- a/business_forms/046_supplier_review_appointment_form--business_forms.xlsx
+++ b/business_forms/046_supplier_review_appointment_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="49" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>supplier_review_appointment_form_business_forms</t>
+          <t>supplier_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Reviewer Information</t>
+          <t>What is the supplier's name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,19 +543,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>reviewer_information</t>
+          <t>supplier_email</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reviewer Information</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>What is the supplier's email address?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -570,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>supplier_details</t>
+          <t>supplier_address</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Supplier Details</t>
+          <t>What is the supplier's address?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -593,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>review_details</t>
+          <t>supplier_job_title</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Review Details</t>
+          <t>What is the supplier's job title?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>supplier_company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>What is the supplier's company name?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -634,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>review_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>What is the review status?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>review_status</t>
+          <t>review_notes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Review Status</t>
+          <t>What are the review notes?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>review_notes</t>
+          <t>reviewer_name</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Review Notes</t>
+          <t>What is the reviewer's name?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -708,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>supplier_email</t>
+          <t>reviewer_phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Supplier Email</t>
+          <t>What is the reviewer's phone number?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reviewer_phone</t>
+          <t>reviewer_job_title</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reviewer Phone</t>
+          <t>What is the reviewer's job title?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reviewer_name</t>
+          <t>reviewer_address</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reviewer Name</t>
+          <t>What is the reviewer's address?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>reviewer_job_title</t>
+          <t>review_details</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Reviewer Job Title</t>
+          <t>What are the review details?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>supplier_company</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Supplier Company</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>supplier_address</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Supplier Address</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>reviewer_address</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Reviewer Address</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>review_notes</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Review Notes</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>review_status</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Review Status</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>supplier_email</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Supplier Email</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>reviewer_phone</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Reviewer Phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>reviewer_name</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Reviewer Name</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>reviewer_job_title</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Reviewer Job Title</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>supplier_company</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Supplier Company</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>supplier_address</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Supplier Address</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>reviewer_address</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Reviewer Address</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>review_details</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Review Details</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1173,57 +870,6 @@
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>Cancelled</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>review_status_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>review_status_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>review_status_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>cancelled</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t>Cancelled</t>
         </is>
